--- a/public/Componentenlijst.xlsx
+++ b/public/Componentenlijst.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_37A3ED4F136DF00E643CCC7756BD2EBFD5D58393" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MIVI\Documents\HOP_Kastconfigurator\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307AB0A5-2C81-4CEB-9C97-E04F213B736D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-3660" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3660" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -224,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,19 +669,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="26" customWidth="1"/>
-    <col min="4" max="5" width="25.7109375" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" customWidth="1"/>
-    <col min="7" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="31.7109375" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" customWidth="1"/>
+    <col min="4" max="5" width="25.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" customWidth="1"/>
+    <col min="7" max="8" width="28.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.6640625" customWidth="1"/>
+    <col min="10" max="10" width="28.5546875" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,7 +692,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" thickBot="1">
+    <row r="2" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -710,7 +715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -730,9 +735,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1"/>
-    <row r="5" spans="1:7" ht="15" customHeight="1" thickBot="1"/>
-    <row r="6" spans="1:7" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -743,7 +748,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" thickBot="1">
+    <row r="7" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -766,7 +771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -782,8 +787,11 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -799,11 +807,14 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="F9">
+        <v>90</v>
+      </c>
       <c r="G9">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" thickBot="1">
+    <row r="10" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -819,8 +830,11 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" thickBot="1">
+      <c r="F10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -836,8 +850,11 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" thickBot="1">
+      <c r="F11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -853,8 +870,11 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -870,8 +890,11 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -887,10 +910,13 @@
       <c r="E14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" thickBot="1"/>
-    <row r="16" spans="1:7" ht="15" customHeight="1" thickBot="1"/>
-    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1">
+      <c r="F14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -906,7 +932,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>1</v>
       </c>
@@ -944,7 +970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1">
+    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -982,7 +1008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1">
+    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1020,7 +1046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1">
+    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -1052,7 +1078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -1090,7 +1116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1">
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -1122,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1">
+    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -1154,7 +1180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1">
+    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1186,9 +1212,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1"/>
-    <row r="27" spans="1:12" ht="15" customHeight="1"/>
-    <row r="28" spans="1:12" ht="15" customHeight="1">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
@@ -1196,7 +1222,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1">
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -1210,7 +1236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1224,7 +1250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -1238,9 +1264,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1"/>
-    <row r="33" spans="1:7" ht="15" customHeight="1"/>
-    <row r="34" spans="1:7" ht="15" customHeight="1">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>56</v>
       </c>
@@ -1248,7 +1274,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1">
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -1262,28 +1288,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>57</v>
       </c>
       <c r="B36" t="s">
         <v>58</v>
       </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
       <c r="D36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>59</v>
       </c>
       <c r="B37" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1"/>
-    <row r="39" spans="1:7" ht="15" customHeight="1"/>
-    <row r="40" spans="1:7" ht="15" customHeight="1">
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
@@ -1294,7 +1326,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1">
+    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>1</v>
       </c>
@@ -1317,7 +1349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>64</v>
       </c>
@@ -1340,7 +1372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>65</v>
       </c>
